--- a/research/traditional_assets/database/data/mexico/mexico_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.0638</v>
+        <v>0.103</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.000408478046394447</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.0003332397281682753</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>68.744</v>
+        <v>-14.5</v>
       </c>
       <c r="L2">
-        <v>0.0505619299794057</v>
+        <v>-0.05261248185776488</v>
       </c>
       <c r="M2">
-        <v>5.34</v>
+        <v>9.078000000000001</v>
       </c>
       <c r="N2">
-        <v>0.003846153846153846</v>
+        <v>0.006178872855976042</v>
       </c>
       <c r="O2">
-        <v>0.07767950657511928</v>
+        <v>-0.6260689655172414</v>
       </c>
       <c r="P2">
-        <v>5.34</v>
+        <v>9.078000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.003846153846153846</v>
+        <v>0.006178872855976042</v>
       </c>
       <c r="R2">
-        <v>0.07767950657511928</v>
+        <v>-0.6260689655172414</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="V2">
-        <v>0.2664938058196485</v>
+        <v>0.255921589980942</v>
       </c>
       <c r="W2">
-        <v>0.1234361968306922</v>
+        <v>-0.03552235849945614</v>
       </c>
       <c r="X2">
-        <v>0.2550424257154977</v>
+        <v>0.1928442511874399</v>
       </c>
       <c r="Y2">
-        <v>-0.1316062288848055</v>
+        <v>-0.2283666096868961</v>
       </c>
       <c r="Z2">
-        <v>0.2055874804272294</v>
+        <v>0.06065274323818747</v>
       </c>
       <c r="AA2">
-        <v>7.611469260337222e-05</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04349302218744359</v>
+        <v>0.08429052800502591</v>
       </c>
       <c r="AC2">
-        <v>-0.04334702866904799</v>
+        <v>-0.08429052800502591</v>
       </c>
       <c r="AD2">
-        <v>8454.1</v>
+        <v>3012.8</v>
       </c>
       <c r="AE2">
-        <v>7.843166240610549</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>8461.94316624061</v>
+        <v>3012.8</v>
       </c>
       <c r="AG2">
-        <v>8091.94316624061</v>
+        <v>2636.8</v>
       </c>
       <c r="AH2">
-        <v>0.8590505958453949</v>
+        <v>0.6721999107541277</v>
       </c>
       <c r="AI2">
-        <v>0.9235163545146566</v>
+        <v>0.8328403593642019</v>
       </c>
       <c r="AJ2">
-        <v>0.8535496051509954</v>
+        <v>0.6421821724305894</v>
       </c>
       <c r="AK2">
-        <v>0.9202979108168776</v>
+        <v>0.8134505630109518</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>3980.273069679849</v>
-      </c>
-      <c r="AP2">
-        <v>3809.766085800663</v>
       </c>
     </row>
     <row r="3">
@@ -715,29 +709,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.108</v>
-      </c>
-      <c r="E3">
-        <v>-0.0638</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0.003660011380343645</v>
-      </c>
-      <c r="J3">
-        <v>0.002790287026560954</v>
-      </c>
       <c r="K3">
-        <v>29.6</v>
-      </c>
-      <c r="L3">
-        <v>0.4603421461897357</v>
+        <v>-53.2</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,7 +719,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,73 +728,67 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="V3">
-        <v>0.01291512915129151</v>
+        <v>0.01079622132253711</v>
       </c>
       <c r="W3">
-        <v>0.1234361968306922</v>
+        <v>-0.1877867984468761</v>
       </c>
       <c r="X3">
-        <v>0.0503676475380887</v>
+        <v>0.0919197564990859</v>
       </c>
       <c r="Y3">
-        <v>0.07306854929260355</v>
+        <v>-0.279706554945962</v>
       </c>
       <c r="Z3">
-        <v>0.11178850534442</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.0003119220161811748</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04349302218744359</v>
+        <v>0.0824569213580664</v>
       </c>
       <c r="AC3">
-        <v>-0.04318110017126242</v>
+        <v>-0.0824569213580664</v>
       </c>
       <c r="AD3">
-        <v>543.3</v>
+        <v>420.9</v>
       </c>
       <c r="AE3">
-        <v>3.093306341219519</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>546.3933063412195</v>
+        <v>420.9</v>
       </c>
       <c r="AG3">
-        <v>533.7933063412195</v>
+        <v>408.9</v>
       </c>
       <c r="AH3">
-        <v>0.3589984949767724</v>
+        <v>0.2746671887235708</v>
       </c>
       <c r="AI3">
-        <v>0.6585485289145021</v>
+        <v>0.6465437788018433</v>
       </c>
       <c r="AJ3">
-        <v>0.3536475907894002</v>
+        <v>0.2689423835832676</v>
       </c>
       <c r="AK3">
-        <v>0.6532831712102003</v>
+        <v>0.639906103286385</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>636.1826697892271</v>
-      </c>
-      <c r="AP3">
-        <v>625.050710001428</v>
       </c>
     </row>
     <row r="4">
@@ -841,10 +808,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.1</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="E4">
-        <v>0.191</v>
+        <v>0.103</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +826,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>38.4</v>
+        <v>38.7</v>
       </c>
       <c r="L4">
-        <v>0.1502347417840376</v>
+        <v>0.1404208998548621</v>
       </c>
       <c r="M4">
-        <v>5.34</v>
+        <v>9.078000000000001</v>
       </c>
       <c r="N4">
-        <v>0.01751393899639226</v>
+        <v>0.02537880905786973</v>
       </c>
       <c r="O4">
-        <v>0.1390625</v>
+        <v>0.2345736434108527</v>
       </c>
       <c r="P4">
-        <v>5.34</v>
+        <v>9.078000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.01751393899639226</v>
+        <v>0.02537880905786973</v>
       </c>
       <c r="R4">
-        <v>0.1390625</v>
+        <v>0.2345736434108527</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,186 +856,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>291.2</v>
+        <v>364</v>
       </c>
       <c r="V4">
-        <v>0.9550672351590686</v>
+        <v>1.017612524461839</v>
       </c>
       <c r="W4">
-        <v>0.1289456010745467</v>
+        <v>0.1167420814479638</v>
       </c>
       <c r="X4">
-        <v>0.2550424257154977</v>
+        <v>0.2937687458757939</v>
       </c>
       <c r="Y4">
-        <v>-0.1260968246409511</v>
+        <v>-0.1770266644278301</v>
       </c>
       <c r="Z4">
-        <v>0.1394055085901282</v>
+        <v>0.0738893804123435</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04334702866904799</v>
+        <v>0.08612413465198543</v>
       </c>
       <c r="AC4">
-        <v>-0.04334702866904799</v>
+        <v>-0.08612413465198543</v>
       </c>
       <c r="AD4">
-        <v>3689.6</v>
+        <v>2591.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3689.6</v>
+        <v>2591.9</v>
       </c>
       <c r="AG4">
-        <v>3398.4</v>
+        <v>2227.9</v>
       </c>
       <c r="AH4">
-        <v>0.9236700463136813</v>
+        <v>0.8787293192297261</v>
       </c>
       <c r="AI4">
-        <v>0.9173545499751368</v>
+        <v>0.8737232428788134</v>
       </c>
       <c r="AJ4">
-        <v>0.9176680258148138</v>
+        <v>0.8616568688118813</v>
       </c>
       <c r="AK4">
-        <v>0.9109038275972982</v>
+        <v>0.856061479346782</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Casa de Bolsa Finamex S.A.B. de C.V. (BMV:FINAMEX O)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.188</v>
-      </c>
-      <c r="E5">
-        <v>-0.396</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0.0003078080408981378</v>
-      </c>
-      <c r="J5">
-        <v>0.0003078080408981378</v>
-      </c>
-      <c r="K5">
-        <v>0.744</v>
-      </c>
-      <c r="L5">
-        <v>0.0007155910358757334</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>66.2</v>
-      </c>
-      <c r="V5">
-        <v>0.6135310472659871</v>
-      </c>
-      <c r="W5">
-        <v>0.009489795918367346</v>
-      </c>
-      <c r="X5">
-        <v>0.7350201467121904</v>
-      </c>
-      <c r="Y5">
-        <v>-0.7255303507938231</v>
-      </c>
-      <c r="Z5">
-        <v>0.2472797409102145</v>
-      </c>
-      <c r="AA5">
-        <v>7.611469260337222e-05</v>
-      </c>
-      <c r="AB5">
-        <v>0.04350916836569046</v>
-      </c>
-      <c r="AC5">
-        <v>-0.04343305367308709</v>
-      </c>
-      <c r="AD5">
-        <v>4221.2</v>
-      </c>
-      <c r="AE5">
-        <v>4.749859899391031</v>
-      </c>
-      <c r="AF5">
-        <v>4225.949859899391</v>
-      </c>
-      <c r="AG5">
-        <v>4159.749859899391</v>
-      </c>
-      <c r="AH5">
-        <v>0.9751029676873706</v>
-      </c>
-      <c r="AI5">
-        <v>0.9802600288176703</v>
-      </c>
-      <c r="AJ5">
-        <v>0.9747167636656716</v>
-      </c>
-      <c r="AK5">
-        <v>0.979952176682636</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>3323.779527559055</v>
-      </c>
-      <c r="AP5">
-        <v>3275.393590471961</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mexico/mexico_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06619999999999999</v>
+        <v>0.12175</v>
       </c>
       <c r="E2">
-        <v>0.103</v>
+        <v>0.128</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,91 +606,94 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>-14.5</v>
+        <v>69.54899999999999</v>
       </c>
       <c r="L2">
-        <v>-0.05261248185776488</v>
+        <v>0.138599043443603</v>
       </c>
       <c r="M2">
-        <v>9.078000000000001</v>
+        <v>8.419</v>
       </c>
       <c r="N2">
-        <v>0.006178872855976042</v>
+        <v>0.005811818307331217</v>
       </c>
       <c r="O2">
-        <v>-0.6260689655172414</v>
+        <v>0.1210513450948252</v>
       </c>
       <c r="P2">
-        <v>9.078000000000001</v>
+        <v>7.476</v>
       </c>
       <c r="Q2">
-        <v>0.006178872855976042</v>
+        <v>0.005160844953748447</v>
       </c>
       <c r="R2">
-        <v>-0.6260689655172414</v>
+        <v>0.1074925592028642</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1120085520845706</v>
       </c>
       <c r="U2">
-        <v>376</v>
+        <v>331.1</v>
       </c>
       <c r="V2">
-        <v>0.255921589980942</v>
+        <v>0.2285655115283722</v>
       </c>
       <c r="W2">
-        <v>-0.03552235849945614</v>
+        <v>0.08933823529411765</v>
       </c>
       <c r="X2">
-        <v>0.1928442511874399</v>
+        <v>0.0819749550566839</v>
       </c>
       <c r="Y2">
-        <v>-0.2283666096868961</v>
+        <v>0.007363280237433753</v>
       </c>
       <c r="Z2">
-        <v>0.06065274323818747</v>
+        <v>0.1534936788623482</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08429052800502591</v>
+        <v>0.06933246459360712</v>
       </c>
       <c r="AC2">
-        <v>-0.08429052800502591</v>
+        <v>-0.06933246459360712</v>
       </c>
       <c r="AD2">
-        <v>3012.8</v>
+        <v>4123.52</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3012.8</v>
+        <v>4123.52</v>
       </c>
       <c r="AG2">
-        <v>2636.8</v>
+        <v>3792.42</v>
       </c>
       <c r="AH2">
-        <v>0.6721999107541277</v>
+        <v>0.7400271350940038</v>
       </c>
       <c r="AI2">
-        <v>0.8328403593642019</v>
+        <v>0.8388606116827582</v>
       </c>
       <c r="AJ2">
-        <v>0.6421821724305894</v>
+        <v>0.7236034207081827</v>
       </c>
       <c r="AK2">
-        <v>0.8134505630109518</v>
+        <v>0.8272229153760917</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-1.13</v>
+      </c>
+      <c r="AQ2">
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Value Grupo Financiero, S.A.B. de C.V. (BMV:VALUEGF O)</t>
+          <t>Alterna Asesoría Internacional, S.A.B. de C.V. (BMV:ALTERNA B)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,17 +712,32 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
       <c r="K3">
-        <v>-53.2</v>
+        <v>2.43</v>
+      </c>
+      <c r="L3">
+        <v>0.09878048780487805</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01993657505285412</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.3880658436213991</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -728,67 +746,73 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>12</v>
+        <v>17.2</v>
       </c>
       <c r="V3">
-        <v>0.01079622132253711</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="W3">
-        <v>-0.1877867984468761</v>
+        <v>0.08933823529411765</v>
       </c>
       <c r="X3">
-        <v>0.0919197564990859</v>
+        <v>0.06853957052127187</v>
       </c>
       <c r="Y3">
-        <v>-0.279706554945962</v>
+        <v>0.02079866477284578</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.8695652173913044</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0824569213580664</v>
+        <v>0.06731664696098894</v>
       </c>
       <c r="AC3">
-        <v>-0.0824569213580664</v>
+        <v>-0.06731664696098894</v>
       </c>
       <c r="AD3">
-        <v>420.9</v>
+        <v>2.72</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>420.9</v>
+        <v>2.72</v>
       </c>
       <c r="AG3">
-        <v>408.9</v>
+        <v>-14.48</v>
       </c>
       <c r="AH3">
-        <v>0.2746671887235708</v>
+        <v>0.0543782487005198</v>
       </c>
       <c r="AI3">
-        <v>0.6465437788018433</v>
+        <v>0.08338442673206622</v>
       </c>
       <c r="AJ3">
-        <v>0.2689423835832676</v>
+        <v>-0.4411943936624009</v>
       </c>
       <c r="AK3">
-        <v>0.639906103286385</v>
+        <v>-0.9390402075226977</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-1.13</v>
+      </c>
+      <c r="AQ3">
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -799,117 +823,233 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Value Grupo Financiero, S.A.B. de C.V. (BMV:VALUEGF O)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.164</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>-0.181</v>
+      </c>
+      <c r="L4">
+        <v>-0.00191129883843717</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>13.5</v>
+      </c>
+      <c r="V4">
+        <v>0.01470588235294118</v>
+      </c>
+      <c r="W4">
+        <v>-0.0007866145154280747</v>
+      </c>
+      <c r="X4">
+        <v>0.0819749550566839</v>
+      </c>
+      <c r="Y4">
+        <v>-0.08276156957211198</v>
+      </c>
+      <c r="Z4">
+        <v>0.1482003129890454</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06933246459360712</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06933246459360712</v>
+      </c>
+      <c r="AD4">
+        <v>669.1</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>669.1</v>
+      </c>
+      <c r="AG4">
+        <v>655.6</v>
+      </c>
+      <c r="AH4">
+        <v>0.4215865414907694</v>
+      </c>
+      <c r="AI4">
+        <v>0.7097698101198685</v>
+      </c>
+      <c r="AJ4">
+        <v>0.416624300965938</v>
+      </c>
+      <c r="AK4">
+        <v>0.7055531640120534</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Corporación Actinver, S. A. B. de C. V. (BMV:ACTINVR B)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.06619999999999999</v>
-      </c>
-      <c r="E4">
-        <v>0.103</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>38.7</v>
-      </c>
-      <c r="L4">
-        <v>0.1404208998548621</v>
-      </c>
-      <c r="M4">
-        <v>9.078000000000001</v>
-      </c>
-      <c r="N4">
-        <v>0.02537880905786973</v>
-      </c>
-      <c r="O4">
-        <v>0.2345736434108527</v>
-      </c>
-      <c r="P4">
-        <v>9.078000000000001</v>
-      </c>
-      <c r="Q4">
-        <v>0.02537880905786973</v>
-      </c>
-      <c r="R4">
-        <v>0.2345736434108527</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>364</v>
-      </c>
-      <c r="V4">
-        <v>1.017612524461839</v>
-      </c>
-      <c r="W4">
-        <v>0.1167420814479638</v>
-      </c>
-      <c r="X4">
-        <v>0.2937687458757939</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1770266644278301</v>
-      </c>
-      <c r="Z4">
-        <v>0.0738893804123435</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.08612413465198543</v>
-      </c>
-      <c r="AC4">
-        <v>-0.08612413465198543</v>
-      </c>
-      <c r="AD4">
-        <v>2591.9</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>2591.9</v>
-      </c>
-      <c r="AG4">
-        <v>2227.9</v>
-      </c>
-      <c r="AH4">
-        <v>0.8787293192297261</v>
-      </c>
-      <c r="AI4">
-        <v>0.8737232428788134</v>
-      </c>
-      <c r="AJ4">
-        <v>0.8616568688118813</v>
-      </c>
-      <c r="AK4">
-        <v>0.856061479346782</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="D5">
+        <v>0.0795</v>
+      </c>
+      <c r="E5">
+        <v>0.128</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>67.3</v>
+      </c>
+      <c r="L5">
+        <v>0.1759477124183007</v>
+      </c>
+      <c r="M5">
+        <v>7.476</v>
+      </c>
+      <c r="N5">
+        <v>0.01546865301055245</v>
+      </c>
+      <c r="O5">
+        <v>0.1110846953937593</v>
+      </c>
+      <c r="P5">
+        <v>7.476</v>
+      </c>
+      <c r="Q5">
+        <v>0.01546865301055245</v>
+      </c>
+      <c r="R5">
+        <v>0.1110846953937593</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>300.4</v>
+      </c>
+      <c r="V5">
+        <v>0.6215601075936271</v>
+      </c>
+      <c r="W5">
+        <v>0.1799465240641711</v>
+      </c>
+      <c r="X5">
+        <v>0.2103142637830545</v>
+      </c>
+      <c r="Y5">
+        <v>-0.0303677397188834</v>
+      </c>
+      <c r="Z5">
+        <v>0.1470079557246627</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.07143294514882341</v>
+      </c>
+      <c r="AC5">
+        <v>-0.07143294514882341</v>
+      </c>
+      <c r="AD5">
+        <v>3451.7</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>3451.7</v>
+      </c>
+      <c r="AG5">
+        <v>3151.3</v>
+      </c>
+      <c r="AH5">
+        <v>0.8771791613722998</v>
+      </c>
+      <c r="AI5">
+        <v>0.8759992893942086</v>
+      </c>
+      <c r="AJ5">
+        <v>0.8670280085841633</v>
+      </c>
+      <c r="AK5">
+        <v>0.8657655430094233</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>
